--- a/data/trans_camb/P1426-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1426-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,59</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,07</t>
+          <t>8,95</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,88</t>
+          <t>8,45</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,89</t>
+          <t>-1,4; 1,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,4</t>
+          <t>5,43; 10,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,97</t>
+          <t>-1,16; 1,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,15</t>
+          <t>6,99; 10,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,35</t>
+          <t>-0,96; 1,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,44</t>
+          <t>7,06; 10,04</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>281,38%</t>
+          <t>253,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>272,51%</t>
+          <t>269,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>276,43%</t>
+          <t>263,11%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 84,79</t>
+          <t>-37,35; 83,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>141,25; 492,41</t>
+          <t>132,75; 452,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 76,34</t>
+          <t>-29,97; 69,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165,53; 417,03</t>
+          <t>167,31; 411,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 45,88</t>
+          <t>-25,34; 53,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>188,45; 393,7</t>
+          <t>179,47; 375,92</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,75</t>
+          <t>-0,49; 0,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,0</t>
+          <t>1,69; 3,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,28</t>
+          <t>-0,19; 1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,14</t>
+          <t>0,87; 2,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,72</t>
+          <t>-0,23; 0,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,43</t>
+          <t>1,53; 2,65</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>239,45%</t>
+          <t>274,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156,78%</t>
+          <t>182,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>199,33%</t>
+          <t>230,16%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 117,83</t>
+          <t>-42,6; 122,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>100,9; 481,13</t>
+          <t>126,21; 537,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 265,71</t>
+          <t>-18,95; 225,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,39; 407,99</t>
+          <t>60,22; 424,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 104,11</t>
+          <t>-20,99; 112,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100,5; 361,55</t>
+          <t>133,86; 424,07</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,92</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,03</t>
+          <t>-1,95; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,11</t>
+          <t>0,04; 4,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,87</t>
+          <t>-1,54; 1,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,58</t>
+          <t>-0,13; 2,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,06</t>
+          <t>-1,12; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,88</t>
+          <t>0,55; 2,9</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>232,03%</t>
+          <t>230,53%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>102,21%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>152,02%</t>
+          <t>159,12%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 2055,61</t>
+          <t>-18,79; 1668,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,54; 369,02</t>
+          <t>-73,29; 282,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 487,28</t>
+          <t>-11,35; 504,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 185,33</t>
+          <t>-64,31; 155,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,13; 480,55</t>
+          <t>20,31; 448,07</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,96</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,43</t>
+          <t>-0,75; 0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,71</t>
+          <t>2,39; 3,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,81</t>
+          <t>-0,43; 0,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,24</t>
+          <t>2,1; 3,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,51</t>
+          <t>-0,45; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,29</t>
+          <t>2,41; 3,49</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188,42%</t>
+          <t>201,07%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135,95%</t>
+          <t>151,68%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>159,27%</t>
+          <t>173,66%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 34,94</t>
+          <t>-38,96; 43,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>99,2; 302,89</t>
+          <t>122,39; 319,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 52,04</t>
+          <t>-20,82; 56,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,49; 222,61</t>
+          <t>92,61; 237,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 36,02</t>
+          <t>-23,08; 31,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,79; 218,27</t>
+          <t>120,07; 234,83</t>
         </is>
       </c>
     </row>
